--- a/templates/reisekostenabrechnung-vorlage.xlsx
+++ b/templates/reisekostenabrechnung-vorlage.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Saetze 2026" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Abrechnung!$A$1:$I$77</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Abrechnung!$A$1:$I$78</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +29,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="F33" authorId="0">
+    <comment ref="F34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -920,7 +920,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -1262,81 +1262,72 @@
       <c r="I29" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13" t="s">
+      <c r="A30" s="8"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="16"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12"/>
+      <c r="B31" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="14" t="n">
-        <f aca="false">SUM(I23:I29)</f>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="14" t="n">
+        <f aca="false">SUM(I23:I30)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B34" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D34" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E34" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F34" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G34" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H34" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I34" s="7" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="11" t="str">
-        <f aca="false">IF($A34="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B34,'Saetze 2026'!$B$5:$B$7,0),MATCH($C34,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
-        <v/>
-      </c>
-      <c r="E34" s="11" t="str">
-        <f aca="false">IF($A34="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B34,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F34)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G34)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H34)="x",'Saetze 2026'!$B$12,0)))</f>
-        <v/>
-      </c>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="11" t="str">
-        <f aca="false">IF($A34="","",MAX(0,$D34-$E34))</f>
-        <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1440,58 +1431,67 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13" t="s">
+      <c r="A40" s="8"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="11" t="str">
+        <f aca="false">IF($A40="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B40,'Saetze 2026'!$B$5:$B$7,0),MATCH($C40,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
+        <v/>
+      </c>
+      <c r="E40" s="11" t="str">
+        <f aca="false">IF($A40="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B40,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F40)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G40)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H40)="x",'Saetze 2026'!$B$12,0)))</f>
+        <v/>
+      </c>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="11" t="str">
+        <f aca="false">IF($A40="","",MAX(0,$D40-$E40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="12"/>
+      <c r="B41" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="14" t="n">
-        <f aca="false">SUM(I34:I39)</f>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="14" t="n">
+        <f aca="false">SUM(I35:I40)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B44" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="I44" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="16"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8"/>
@@ -1516,58 +1516,58 @@
       <c r="I46" s="16"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12"/>
-      <c r="B47" s="13" t="s">
+      <c r="A47" s="8"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="16"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="12"/>
+      <c r="B48" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="14" t="n">
-        <f aca="false">SUM(I44:I46)</f>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="14" t="n">
+        <f aca="false">SUM(I45:I47)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-    </row>
-    <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B51" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C51" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="I51" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="16"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8"/>
@@ -1603,119 +1603,117 @@
       <c r="I54" s="16"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12"/>
-      <c r="B55" s="13" t="s">
+      <c r="A55" s="8"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="16"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="12"/>
+      <c r="B56" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="14" t="n">
-        <f aca="false">SUM(I51:I54)</f>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="14" t="n">
+        <f aca="false">SUM(I52:I55)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I58" s="18" t="n">
-        <f aca="false">I19+I30+I40+I47+I55</f>
+      <c r="I59" s="18" t="n">
+        <f aca="false">I19+I31+I41+I48+I56</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I59" s="16"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I60" s="16"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="I60" s="16"/>
-    </row>
-    <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="20"/>
-      <c r="B61" s="21" t="s">
+      <c r="I61" s="16"/>
+    </row>
+    <row r="62" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="20"/>
+      <c r="B62" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="22" t="n">
-        <f aca="false">I58-N(I59)-N(I60)</f>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="22" t="n">
+        <f aca="false">I59-N(I60)-N(I61)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="19" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E65" s="19" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E66" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="s">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-    </row>
-    <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="23" t="s">
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+    </row>
+    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B69" s="24" t="s">
+      <c r="B70" s="24" t="s">
         <v>51</v>
-      </c>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="24"/>
-    </row>
-    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="23"/>
-      <c r="B70" s="24" t="s">
-        <v>52</v>
       </c>
       <c r="C70" s="24"/>
       <c r="D70" s="24"/>
@@ -1728,7 +1726,7 @@
     <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="23"/>
       <c r="B71" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C71" s="24"/>
       <c r="D71" s="24"/>
@@ -1739,11 +1737,9 @@
       <c r="I71" s="24"/>
     </row>
     <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="23" t="s">
-        <v>54</v>
-      </c>
+      <c r="A72" s="23"/>
       <c r="B72" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C72" s="24"/>
       <c r="D72" s="24"/>
@@ -1755,10 +1751,10 @@
     </row>
     <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C73" s="24"/>
       <c r="D73" s="24"/>
@@ -1770,10 +1766,10 @@
     </row>
     <row r="74" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C74" s="24"/>
       <c r="D74" s="24"/>
@@ -1785,10 +1781,10 @@
     </row>
     <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C75" s="24"/>
       <c r="D75" s="24"/>
@@ -1800,10 +1796,10 @@
     </row>
     <row r="76" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C76" s="24"/>
       <c r="D76" s="24"/>
@@ -1813,8 +1809,23 @@
       <c r="H76" s="24"/>
       <c r="I76" s="24"/>
     </row>
+    <row r="77" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B4:E4"/>
@@ -1838,19 +1849,19 @@
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="D29:H29"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A43:I43"/>
     <mergeCell ref="D45:H45"/>
     <mergeCell ref="D46:H46"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="A50:I50"/>
     <mergeCell ref="D52:H52"/>
     <mergeCell ref="D53:H53"/>
     <mergeCell ref="D54:H54"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="B70:I70"/>
     <mergeCell ref="B71:I71"/>
     <mergeCell ref="B72:I72"/>
@@ -1858,21 +1869,22 @@
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="B75:I75"/>
     <mergeCell ref="B76:I76"/>
+    <mergeCell ref="B77:I77"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15:C18" type="list">
       <formula1>'Saetze 2026'!$A$15:$A$17</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B34:B39" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B35:B40" type="list">
       <formula1>'Saetze 2026'!$B$5:$B$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34:C39" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35:C40" type="list">
       <formula1>'Saetze 2026'!$C$4:$F$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F34:H39" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F35:H40" type="list">
       <formula1>"x"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/templates/reisekostenabrechnung-vorlage.xlsx
+++ b/templates/reisekostenabrechnung-vorlage.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t xml:space="preserve">Reisekostenabrechnung</t>
   </si>
@@ -91,10 +91,7 @@
     <t xml:space="preserve">Inland und Ausland · Stand 2026 · Sätze siehe Blatt „Saetze 2026“</t>
   </si>
   <si>
-    <t xml:space="preserve">Firma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coldewey Holding</t>
+    <t xml:space="preserve">Abrechnung an</t>
   </si>
   <si>
     <t xml:space="preserve">Gelb = ausfüllen</t>
@@ -107,9 +104,6 @@
   </si>
   <si>
     <t xml:space="preserve">Funktion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Managing Director</t>
   </si>
   <si>
     <t xml:space="preserve">Reisezweck</t>
@@ -962,42 +956,38 @@
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="G4" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="G5" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1006,7 +996,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1015,7 +1005,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1024,7 +1014,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1033,7 +1023,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1042,7 +1032,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1055,22 +1045,22 @@
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="I14" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1144,7 +1134,7 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12"/>
       <c r="B19" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -1159,7 +1149,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1172,16 +1162,16 @@
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1275,7 +1265,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12"/>
       <c r="B31" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -1290,7 +1280,7 @@
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1303,31 +1293,31 @@
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="E34" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="F34" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="G34" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="H34" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="I34" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1453,7 +1443,7 @@
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12"/>
       <c r="B41" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
@@ -1468,7 +1458,7 @@
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1481,16 +1471,16 @@
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1529,7 +1519,7 @@
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12"/>
       <c r="B48" s="13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
@@ -1544,7 +1534,7 @@
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1557,16 +1547,16 @@
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1616,7 +1606,7 @@
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12"/>
       <c r="B56" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C56" s="12"/>
       <c r="D56" s="12"/>
@@ -1631,7 +1621,7 @@
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -1644,7 +1634,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I59" s="18" t="n">
         <f aca="false">I19+I31+I41+I48+I56</f>
@@ -1653,20 +1643,20 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I60" s="16"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I61" s="16"/>
     </row>
     <row r="62" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="20"/>
       <c r="B62" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
@@ -1681,23 +1671,23 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -1710,10 +1700,10 @@
     </row>
     <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C70" s="24"/>
       <c r="D70" s="24"/>
@@ -1726,7 +1716,7 @@
     <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="23"/>
       <c r="B71" s="24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C71" s="24"/>
       <c r="D71" s="24"/>
@@ -1739,7 +1729,7 @@
     <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="23"/>
       <c r="B72" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C72" s="24"/>
       <c r="D72" s="24"/>
@@ -1751,10 +1741,10 @@
     </row>
     <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C73" s="24"/>
       <c r="D73" s="24"/>
@@ -1766,10 +1756,10 @@
     </row>
     <row r="74" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C74" s="24"/>
       <c r="D74" s="24"/>
@@ -1781,10 +1771,10 @@
     </row>
     <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C75" s="24"/>
       <c r="D75" s="24"/>
@@ -1796,10 +1786,10 @@
     </row>
     <row r="76" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C76" s="24"/>
       <c r="D76" s="24"/>
@@ -1811,10 +1801,10 @@
     </row>
     <row r="77" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C77" s="24"/>
       <c r="D77" s="24"/>
@@ -1917,43 +1907,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>28</v>
@@ -1968,15 +1958,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>66</v>
@@ -1996,10 +1986,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>52</v>
@@ -2019,12 +2009,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B10" s="27" t="n">
         <v>0.2</v>
@@ -2032,7 +2022,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B11" s="27" t="n">
         <v>0.4</v>
@@ -2040,7 +2030,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B12" s="27" t="n">
         <v>0.4</v>
@@ -2048,12 +2038,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" s="28" t="n">
         <v>0.3</v>
@@ -2061,7 +2051,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C16" s="28" t="n">
         <v>0.2</v>
@@ -2069,7 +2059,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>0.05</v>
@@ -2077,42 +2067,42 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
